--- a/UTCUTS/A1_Outputs/A-O_Demand_COMPLETED.xlsx
+++ b/UTCUTS/A1_Outputs/A-O_Demand_COMPLETED.xlsx
@@ -20577,7 +20577,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E475013-FE45-4A7C-97D0-B63A923F1242}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61F91BFC-D074-49C9-B310-2E4D7DD8B3FE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
